--- a/outputs/per-fund/vc-investments-cyber-fund.xlsx
+++ b/outputs/per-fund/vc-investments-cyber-fund.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only cyber•Fund. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only cyber•Fund. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -5954,11 +5954,11 @@
         <v>3</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, dragonfly, figment-capital, founders-fund</t>
+          <t>alliance-dao, cyber-fund, dragonfly, figment-capital, foresight-ventures, founders-fund, hashkey-capital, longhash-ventures, mirana-ventures, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -6143,11 +6143,11 @@
         <v>1</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, delphi-ventures</t>
+          <t>alliance-dao, cyber-fund, delphi-ventures, longhash-ventures</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -6202,11 +6202,11 @@
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, founders-fund, framework-ventures</t>
+          <t>cyber-fund, founders-fund, framework-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -6324,11 +6324,11 @@
         <v>3</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, figment-capital</t>
+          <t>1kx, cyber-fund, figment-capital, gsr, hashkey-capital</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -6576,11 +6576,11 @@
         <v>2</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund</t>
+          <t>cyber-fund, mirana-ventures</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -6761,11 +6761,11 @@
         <v>2</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, cyber-fund, maven11, robot-ventures</t>
+          <t>arrington-capital, coinbase-ventures, cyber-fund, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -6887,11 +6887,11 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, maven11</t>
+          <t>cyber-fund, digital-currency-group, maven11</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -6950,11 +6950,11 @@
         <v>2</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund</t>
+          <t>blockchain-capital, cyber-fund, mirana-ventures</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -7139,11 +7139,11 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, delphi-ventures</t>
+          <t>animoca-brands, cyber-fund, delphi-ventures, hashkey-capital</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -7202,11 +7202,11 @@
         <v>2</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, cyber-fund</t>
+          <t>coinbase-ventures, cyber-fund, gsr</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -7322,11 +7322,11 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, delphi-ventures</t>
+          <t>cyber-fund, delphi-ventures, gsr</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -7448,11 +7448,11 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, maven11</t>
+          <t>cyber-fund, hashed, maven11</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -9173,19 +9173,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
